--- a/data/trans_bre/P44D-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P44D-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-41,94; 52,77</t>
+          <t>-40,61; 49,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-45,13; -4,89</t>
+          <t>-44,66; -7,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 10,26</t>
+          <t>-5,32; 8,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-71,68; 472,82</t>
+          <t>-66,79; 330,39</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-25,59%</t>
+          <t>-26,81%</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,58; 18,32</t>
+          <t>-25,06; 17,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,78</t>
+          <t>0,0; 76,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 6,42</t>
+          <t>-12,62; 6,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,55; 151,72</t>
+          <t>-84,86; 149,21</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,32</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>49,7%</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-50,59; 0,0</t>
+          <t>-44,08; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 14,95</t>
+          <t>-25,71; 14,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 12,03</t>
+          <t>-4,66; 11,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,07; 450,58</t>
+          <t>-52,32; 376,79</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,92; 6,3</t>
+          <t>-69,54; 6,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 26,37</t>
+          <t>-23,75; 24,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 11,91</t>
+          <t>-6,12; 12,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 441,08</t>
+          <t>-100,0; 337,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 240,82</t>
+          <t>-44,72; 265,92</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>-4,64</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-62,46%</t>
+          <t>-62,04%</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-66,1; 0,0</t>
+          <t>-51,25; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 4,61</t>
+          <t>-19,77; 2,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-1,82</t>
+          <t>-1,83</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-43,69%</t>
+          <t>-43,25%</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-54,08; 0,0</t>
+          <t>-41,4; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,42; 0,0</t>
+          <t>-49,18; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 3,01</t>
+          <t>-9,24; 2,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-11,61</t>
+          <t>-10,87</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-61,0%</t>
+          <t>-58,81%</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1114,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 54,18</t>
+          <t>-8,32; 56,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 12,66</t>
+          <t>-17,67; 11,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,9; -3,41</t>
+          <t>-18,8; -3,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-59,76; —</t>
+          <t>-49,72; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-81,3; -22,37</t>
+          <t>-79,29; -25,8</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>-2,02</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>105,51%</t>
+          <t>-27,55%</t>
         </is>
       </c>
     </row>
@@ -1194,17 +1194,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,67</t>
+          <t>0,0; 44,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 57,56</t>
+          <t>-10,98; 55,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 8,75</t>
+          <t>-7,17; 2,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-57,13; 803,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 1199,13</t>
+          <t>-67,1; 56,19</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>-2,56</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>-26,02%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 16,28</t>
+          <t>-5,21; 16,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 5,69</t>
+          <t>-11,34; 6,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 5,77</t>
+          <t>-5,35; 0,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-35,66; 218,21</t>
+          <t>-32,65; 213,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-62,29; 61,65</t>
+          <t>-64,23; 66,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 186,95</t>
+          <t>-46,64; 1,34</t>
         </is>
       </c>
     </row>
